--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/148.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/148.xlsx
@@ -426,13 +426,13 @@
         <v>4.168950565539638</v>
       </c>
       <c r="E2">
-        <v>-16.22488593135541</v>
+        <v>-16.99581334642121</v>
       </c>
       <c r="F2">
-        <v>-0.4494855538849643</v>
+        <v>-0.7273671977258781</v>
       </c>
       <c r="G2">
-        <v>-3.198623766347841</v>
+        <v>-6.342288015529906</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>4.480631871178508</v>
       </c>
       <c r="E3">
-        <v>-15.74030298474262</v>
+        <v>-16.16391002884213</v>
       </c>
       <c r="F3">
-        <v>-0.8629112991111556</v>
+        <v>-0.7044876900605557</v>
       </c>
       <c r="G3">
-        <v>-3.867420176191406</v>
+        <v>-4.054694426802437</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>4.807974642086253</v>
       </c>
       <c r="E4">
-        <v>-16.05835582819734</v>
+        <v>-17.09128263545092</v>
       </c>
       <c r="F4">
-        <v>-1.52445130555866</v>
+        <v>-0.2952435434836964</v>
       </c>
       <c r="G4">
-        <v>-3.826051599132673</v>
+        <v>-5.960459624666986</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>5.126760482169247</v>
       </c>
       <c r="E5">
-        <v>-17.54327868310451</v>
+        <v>-18.54648964391976</v>
       </c>
       <c r="F5">
-        <v>-0.6250986149110567</v>
+        <v>-0.5727383397475028</v>
       </c>
       <c r="G5">
-        <v>-3.840098243855801</v>
+        <v>-5.350832595246814</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>5.444380906342628</v>
       </c>
       <c r="E6">
-        <v>-15.20795822277093</v>
+        <v>-18.53918068687138</v>
       </c>
       <c r="F6">
-        <v>-0.9301449109919746</v>
+        <v>-0.7020514615289224</v>
       </c>
       <c r="G6">
-        <v>-3.836003099023722</v>
+        <v>-4.763733828221383</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>5.755976649839377</v>
       </c>
       <c r="E7">
-        <v>-16.5588608894211</v>
+        <v>-18.69676252539029</v>
       </c>
       <c r="F7">
-        <v>-0.4571313850128037</v>
+        <v>-0.3449306770384163</v>
       </c>
       <c r="G7">
-        <v>-3.154302182668078</v>
+        <v>-4.878407815156198</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>6.066282394760838</v>
       </c>
       <c r="E8">
-        <v>-18.83737617180246</v>
+        <v>-19.59135803713156</v>
       </c>
       <c r="F8">
-        <v>-0.4270956113546965</v>
+        <v>-0.2723135054068032</v>
       </c>
       <c r="G8">
-        <v>-3.600414746812567</v>
+        <v>-4.842703581515158</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>6.376007758895785</v>
       </c>
       <c r="E9">
-        <v>-19.41163196071514</v>
+        <v>-19.89687153605904</v>
       </c>
       <c r="F9">
-        <v>-0.8076459394659837</v>
+        <v>-0.08959719390170508</v>
       </c>
       <c r="G9">
-        <v>-2.692818755584753</v>
+        <v>-4.946850033635091</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>6.687382367009747</v>
       </c>
       <c r="E10">
-        <v>-20.30335641993555</v>
+        <v>-20.78560720243439</v>
       </c>
       <c r="F10">
-        <v>-1.092099850280709</v>
+        <v>-0.2582842750729908</v>
       </c>
       <c r="G10">
-        <v>-3.781806158000314</v>
+        <v>-4.890534343466548</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>6.99926927662969</v>
       </c>
       <c r="E11">
-        <v>-20.17833430953179</v>
+        <v>-22.97610253552866</v>
       </c>
       <c r="F11">
-        <v>-0.9215182928592206</v>
+        <v>-0.07489615760422225</v>
       </c>
       <c r="G11">
-        <v>-2.982190230626908</v>
+        <v>-4.041323133369321</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>7.317268481495644</v>
       </c>
       <c r="E12">
-        <v>-20.74066209790826</v>
+        <v>-22.58088902345725</v>
       </c>
       <c r="F12">
-        <v>-0.8251973879964997</v>
+        <v>-0.2064168785141026</v>
       </c>
       <c r="G12">
-        <v>-2.106987927500863</v>
+        <v>-3.002159441319792</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>7.639174034974921</v>
       </c>
       <c r="E13">
-        <v>-22.50442121136373</v>
+        <v>-22.65347140485219</v>
       </c>
       <c r="F13">
-        <v>-0.3106230126840719</v>
+        <v>-0.3392754127795041</v>
       </c>
       <c r="G13">
-        <v>-1.569352021377683</v>
+        <v>-2.875388720984481</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>7.962345410295302</v>
       </c>
       <c r="E14">
-        <v>-23.31955558969241</v>
+        <v>-23.13212657898894</v>
       </c>
       <c r="F14">
-        <v>-0.09469910873554724</v>
+        <v>0.07206450332643803</v>
       </c>
       <c r="G14">
-        <v>-1.532667866257019</v>
+        <v>-3.035539671992264</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>8.277017335410296</v>
       </c>
       <c r="E15">
-        <v>-24.60804229909485</v>
+        <v>-25.21181921006353</v>
       </c>
       <c r="F15">
-        <v>-0.3634803082893056</v>
+        <v>-0.2570665749908755</v>
       </c>
       <c r="G15">
-        <v>-1.790784480862915</v>
+        <v>-3.013802629981409</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>8.569007814472085</v>
       </c>
       <c r="E16">
-        <v>-24.85448185459228</v>
+        <v>-25.76663426006128</v>
       </c>
       <c r="F16">
-        <v>-0.1729814850349061</v>
+        <v>-0.01278848321192652</v>
       </c>
       <c r="G16">
-        <v>-0.6094957582669344</v>
+        <v>-2.731509101302215</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>8.821774534641948</v>
       </c>
       <c r="E17">
-        <v>-26.61930063096554</v>
+        <v>-27.80129574560361</v>
       </c>
       <c r="F17">
-        <v>-0.205002026990121</v>
+        <v>0.05815869973564274</v>
       </c>
       <c r="G17">
-        <v>0.3102565561810832</v>
+        <v>-1.515456339998348</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>9.027103931392128</v>
       </c>
       <c r="E18">
-        <v>-27.08206991828338</v>
+        <v>-28.03144638009543</v>
       </c>
       <c r="F18">
-        <v>-0.4344506855241533</v>
+        <v>0.1365984658415335</v>
       </c>
       <c r="G18">
-        <v>0.5646421859642204</v>
+        <v>-2.089703569240328</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>9.176575576114425</v>
       </c>
       <c r="E19">
-        <v>-28.2403041298032</v>
+        <v>-28.71814417861857</v>
       </c>
       <c r="F19">
-        <v>-0.3889385236795428</v>
+        <v>0.4378748618723109</v>
       </c>
       <c r="G19">
-        <v>0.1140868697060297</v>
+        <v>-0.5166978562556237</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>9.27121960519545</v>
       </c>
       <c r="E20">
-        <v>-28.63870568757602</v>
+        <v>-28.61708222418939</v>
       </c>
       <c r="F20">
-        <v>-0.4813048025612989</v>
+        <v>0.2491305207770408</v>
       </c>
       <c r="G20">
-        <v>1.657003034284299</v>
+        <v>-0.1611750602477517</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>9.31242310812601</v>
       </c>
       <c r="E21">
-        <v>-28.38087701994931</v>
+        <v>-30.11644864694403</v>
       </c>
       <c r="F21">
-        <v>-0.2375734332681976</v>
+        <v>1.00956682634257</v>
       </c>
       <c r="G21">
-        <v>0.9410181083239617</v>
+        <v>-0.13192970095383</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>9.302633605799633</v>
       </c>
       <c r="E22">
-        <v>-30.41926543959994</v>
+        <v>-29.92784902570958</v>
       </c>
       <c r="F22">
-        <v>-0.3923141208459508</v>
+        <v>0.6981180786054147</v>
       </c>
       <c r="G22">
-        <v>1.057747944038664</v>
+        <v>-0.4308984475143324</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>9.244422047513421</v>
       </c>
       <c r="E23">
-        <v>-29.17655707394103</v>
+        <v>-31.88812806143891</v>
       </c>
       <c r="F23">
-        <v>0.01839540766646087</v>
+        <v>0.3086338080549348</v>
       </c>
       <c r="G23">
-        <v>1.407586533355607</v>
+        <v>0.0444164388320676</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>9.145550434746685</v>
       </c>
       <c r="E24">
-        <v>-31.17010454396771</v>
+        <v>-31.40346133805698</v>
       </c>
       <c r="F24">
-        <v>0.0719650992381021</v>
+        <v>0.6096153052903156</v>
       </c>
       <c r="G24">
-        <v>1.971627350700014</v>
+        <v>0.7095447642181203</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>9.010696308554932</v>
       </c>
       <c r="E25">
-        <v>-30.24921671213791</v>
+        <v>-31.91371620381925</v>
       </c>
       <c r="F25">
-        <v>-0.2766881136609874</v>
+        <v>0.6201074068141742</v>
       </c>
       <c r="G25">
-        <v>2.802395511597962</v>
+        <v>0.8564800174331327</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>8.850525151378275</v>
       </c>
       <c r="E26">
-        <v>-30.8047065047628</v>
+        <v>-32.26423820590897</v>
       </c>
       <c r="F26">
-        <v>-0.07285671705852988</v>
+        <v>0.5115879635778278</v>
       </c>
       <c r="G26">
-        <v>2.216683863153485</v>
+        <v>0.08289490963501661</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>8.671730733154961</v>
       </c>
       <c r="E27">
-        <v>-30.68022781123996</v>
+        <v>-32.82038462726497</v>
       </c>
       <c r="F27">
-        <v>0.05595524244419605</v>
+        <v>0.4884872818159579</v>
       </c>
       <c r="G27">
-        <v>1.590424652944016</v>
+        <v>-0.3048096995601107</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>8.479257108304456</v>
       </c>
       <c r="E28">
-        <v>-30.2735934877212</v>
+        <v>-31.36981704041699</v>
       </c>
       <c r="F28">
-        <v>-0.3484205889064106</v>
+        <v>0.3967836968564414</v>
       </c>
       <c r="G28">
-        <v>2.001084584908449</v>
+        <v>0.008430808820189799</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>8.276909899631692</v>
       </c>
       <c r="E29">
-        <v>-29.59165964385414</v>
+        <v>-30.68350642642151</v>
       </c>
       <c r="F29">
-        <v>0.05713152415617135</v>
+        <v>0.6005587644755086</v>
       </c>
       <c r="G29">
-        <v>1.645538615081802</v>
+        <v>-0.3223158643717767</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>8.070832946040243</v>
       </c>
       <c r="E30">
-        <v>-29.4105659682874</v>
+        <v>-31.76545849328213</v>
       </c>
       <c r="F30">
-        <v>0.2349936026808644</v>
+        <v>0.106588371572913</v>
       </c>
       <c r="G30">
-        <v>2.440652200521799</v>
+        <v>-0.4630074286997236</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>7.863734923760641</v>
       </c>
       <c r="E31">
-        <v>-29.38314605817095</v>
+        <v>-30.51226671029547</v>
       </c>
       <c r="F31">
-        <v>0.04688627611834707</v>
+        <v>1.029436046866119</v>
       </c>
       <c r="G31">
-        <v>1.074244392460852</v>
+        <v>-0.2892236511612219</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>7.663562980338043</v>
       </c>
       <c r="E32">
-        <v>-28.62047405122113</v>
+        <v>-29.77844108277451</v>
       </c>
       <c r="F32">
-        <v>-0.17391174162825</v>
+        <v>0.4673258081440417</v>
       </c>
       <c r="G32">
-        <v>0.6250132944183698</v>
+        <v>-1.719011853571516</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>7.472958518263351</v>
       </c>
       <c r="E33">
-        <v>-27.97137617238369</v>
+        <v>-30.48751633560654</v>
       </c>
       <c r="F33">
-        <v>-0.6037408181646771</v>
+        <v>1.033367478559805</v>
       </c>
       <c r="G33">
-        <v>1.945781921674924</v>
+        <v>-0.7383057746544369</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>7.292330435582228</v>
       </c>
       <c r="E34">
-        <v>-28.18232154860899</v>
+        <v>-30.30557809963738</v>
       </c>
       <c r="F34">
-        <v>-0.4091647705536984</v>
+        <v>0.1222503140576433</v>
       </c>
       <c r="G34">
-        <v>0.02329515829151743</v>
+        <v>-1.623108659844369</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>7.121906061179354</v>
       </c>
       <c r="E35">
-        <v>-26.99097513514508</v>
+        <v>-28.37139439537724</v>
       </c>
       <c r="F35">
-        <v>-0.09304734413436502</v>
+        <v>0.6486562609842563</v>
       </c>
       <c r="G35">
-        <v>0.3320664301938018</v>
+        <v>-1.379723972888229</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>6.962454263296636</v>
       </c>
       <c r="E36">
-        <v>-28.1279526896729</v>
+        <v>-27.32781208878362</v>
       </c>
       <c r="F36">
-        <v>-0.07162493473056701</v>
+        <v>0.584460272369503</v>
       </c>
       <c r="G36">
-        <v>0.0898007076299363</v>
+        <v>-1.247374983319246</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>6.813282114710097</v>
       </c>
       <c r="E37">
-        <v>-26.05822270141518</v>
+        <v>-27.01105438889509</v>
       </c>
       <c r="F37">
-        <v>0.5100927604157746</v>
+        <v>0.9671047132750674</v>
       </c>
       <c r="G37">
-        <v>-1.140172897666566</v>
+        <v>-2.839045552054361</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>6.677387631934484</v>
       </c>
       <c r="E38">
-        <v>-26.24502678270559</v>
+        <v>-26.24802916097267</v>
       </c>
       <c r="F38">
-        <v>-0.2134414340898424</v>
+        <v>0.5688969056057059</v>
       </c>
       <c r="G38">
-        <v>-1.662480977942921</v>
+        <v>-1.666784687143973</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>6.553010060852744</v>
       </c>
       <c r="E39">
-        <v>-24.18724743735411</v>
+        <v>-25.85630257388716</v>
       </c>
       <c r="F39">
-        <v>0.9135822386453858</v>
+        <v>0.8980023045335327</v>
       </c>
       <c r="G39">
-        <v>-0.01084318730944705</v>
+        <v>-2.765809663634604</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>6.436098500659446</v>
       </c>
       <c r="E40">
-        <v>-23.95863195555088</v>
+        <v>-24.46228883468397</v>
       </c>
       <c r="F40">
-        <v>0.8692761797392514</v>
+        <v>0.8809627870579468</v>
       </c>
       <c r="G40">
-        <v>-0.01469997286269798</v>
+        <v>-2.307765893366582</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>6.322487389033819</v>
       </c>
       <c r="E41">
-        <v>-23.98157320487374</v>
+        <v>-23.50880957542097</v>
       </c>
       <c r="F41">
-        <v>0.6291531788527448</v>
+        <v>1.266788158790261</v>
       </c>
       <c r="G41">
-        <v>-2.015875093169042</v>
+        <v>-2.518545017306439</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>6.208642003065386</v>
       </c>
       <c r="E42">
-        <v>-22.33481627435445</v>
+        <v>-24.77744345477378</v>
       </c>
       <c r="F42">
-        <v>0.4691929482699518</v>
+        <v>1.336819995757737</v>
       </c>
       <c r="G42">
-        <v>-1.390271370976347</v>
+        <v>-2.617957389305214</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>6.090707540809809</v>
       </c>
       <c r="E43">
-        <v>-21.73007932689614</v>
+        <v>-24.37756108600046</v>
       </c>
       <c r="F43">
-        <v>0.7078505672209062</v>
+        <v>1.123044876852074</v>
       </c>
       <c r="G43">
-        <v>-1.913926843287185</v>
+        <v>-3.03360300285179</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>5.967918254325554</v>
       </c>
       <c r="E44">
-        <v>-21.94846951439005</v>
+        <v>-23.18624637185461</v>
       </c>
       <c r="F44">
-        <v>1.033866155736291</v>
+        <v>1.727653676807378</v>
       </c>
       <c r="G44">
-        <v>-2.339282286900444</v>
+        <v>-3.053400065176632</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>5.836287830728861</v>
       </c>
       <c r="E45">
-        <v>-19.6652944322548</v>
+        <v>-21.39573303396183</v>
       </c>
       <c r="F45">
-        <v>0.7253191790111422</v>
+        <v>1.474032429092253</v>
       </c>
       <c r="G45">
-        <v>-2.190794387827513</v>
+        <v>-2.746717747509627</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>5.69074023433996</v>
       </c>
       <c r="E46">
-        <v>-20.15609950215412</v>
+        <v>-20.5138580057081</v>
       </c>
       <c r="F46">
-        <v>0.9569224211598559</v>
+        <v>1.982093351516468</v>
       </c>
       <c r="G46">
-        <v>-2.708924559633307</v>
+        <v>-3.610396041613469</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>5.527086829032186</v>
       </c>
       <c r="E47">
-        <v>-19.21465239832949</v>
+        <v>-19.20801818390826</v>
       </c>
       <c r="F47">
-        <v>1.05188314674718</v>
+        <v>1.980539334268816</v>
       </c>
       <c r="G47">
-        <v>-2.956116373959608</v>
+        <v>-3.832960707673132</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>5.341159195490999</v>
       </c>
       <c r="E48">
-        <v>-17.4923786352583</v>
+        <v>-19.61060405166416</v>
       </c>
       <c r="F48">
-        <v>1.679016913119407</v>
+        <v>2.436123181725683</v>
       </c>
       <c r="G48">
-        <v>-2.02006293327622</v>
+        <v>-3.981826008937539</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>5.129471316381688</v>
       </c>
       <c r="E49">
-        <v>-15.83302801852368</v>
+        <v>-18.82976380699557</v>
       </c>
       <c r="F49">
-        <v>1.32940279403307</v>
+        <v>2.213078631582694</v>
       </c>
       <c r="G49">
-        <v>-2.889514818800551</v>
+        <v>-4.530092076787319</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>4.891291951492473</v>
       </c>
       <c r="E50">
-        <v>-16.92700318387466</v>
+        <v>-19.02981367475842</v>
       </c>
       <c r="F50">
-        <v>1.945333719649837</v>
+        <v>2.116512529968744</v>
       </c>
       <c r="G50">
-        <v>-4.187619451295254</v>
+        <v>-3.71477754246669</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>4.624128668654622</v>
       </c>
       <c r="E51">
-        <v>-16.2298989520819</v>
+        <v>-16.93872287460651</v>
       </c>
       <c r="F51">
-        <v>1.460327918780338</v>
+        <v>2.837883028818248</v>
       </c>
       <c r="G51">
-        <v>-4.189688542257299</v>
+        <v>-4.48766081461048</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>4.326490182556841</v>
       </c>
       <c r="E52">
-        <v>-15.05689285834906</v>
+        <v>-17.00902290510159</v>
       </c>
       <c r="F52">
-        <v>1.996798529650965</v>
+        <v>2.593758185008817</v>
       </c>
       <c r="G52">
-        <v>-4.310182468250153</v>
+        <v>-5.315022424148518</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>3.998776122371238</v>
       </c>
       <c r="E53">
-        <v>-13.30197785463057</v>
+        <v>-15.35889678992059</v>
       </c>
       <c r="F53">
-        <v>1.820763829616848</v>
+        <v>2.593619019285147</v>
       </c>
       <c r="G53">
-        <v>-4.508050464586852</v>
+        <v>-5.843584124948555</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>3.642397925652029</v>
       </c>
       <c r="E54">
-        <v>-12.96267288265785</v>
+        <v>-15.67194566959684</v>
       </c>
       <c r="F54">
-        <v>1.709691358045073</v>
+        <v>2.382161672372517</v>
       </c>
       <c r="G54">
-        <v>-4.215474381462682</v>
+        <v>-5.026796397862951</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>3.262192232403717</v>
       </c>
       <c r="E55">
-        <v>-13.69331046447741</v>
+        <v>-14.85237338674064</v>
       </c>
       <c r="F55">
-        <v>2.163080031884521</v>
+        <v>2.255694820987117</v>
       </c>
       <c r="G55">
-        <v>-4.54321507930499</v>
+        <v>-5.545946217694841</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>2.865902241460249</v>
       </c>
       <c r="E56">
-        <v>-12.15968840009175</v>
+        <v>-14.92831589584927</v>
       </c>
       <c r="F56">
-        <v>1.464681817849452</v>
+        <v>2.980289325768317</v>
       </c>
       <c r="G56">
-        <v>-4.754775491992116</v>
+        <v>-5.577710902144148</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>2.460776396911935</v>
       </c>
       <c r="E57">
-        <v>-10.24078829560751</v>
+        <v>-13.03411408860286</v>
       </c>
       <c r="F57">
-        <v>1.841454790603974</v>
+        <v>2.664893407356822</v>
       </c>
       <c r="G57">
-        <v>-5.509033634931966</v>
+        <v>-6.198272663480531</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>2.054866647375055</v>
       </c>
       <c r="E58">
-        <v>-12.55957076886508</v>
+        <v>-13.6983189567299</v>
       </c>
       <c r="F58">
-        <v>2.097559483792691</v>
+        <v>2.579260098725021</v>
       </c>
       <c r="G58">
-        <v>-6.376634925499845</v>
+        <v>-6.938891358798585</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>1.656148429895155</v>
       </c>
       <c r="E59">
-        <v>-11.97584594080236</v>
+        <v>-12.06272471463952</v>
       </c>
       <c r="F59">
-        <v>1.743516912570988</v>
+        <v>2.825712654936318</v>
       </c>
       <c r="G59">
-        <v>-5.355934145922832</v>
+        <v>-7.968643169879966</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>1.271301773908023</v>
       </c>
       <c r="E60">
-        <v>-9.285022156970626</v>
+        <v>-11.71334388799973</v>
       </c>
       <c r="F60">
-        <v>2.231610867118124</v>
+        <v>3.008551564817031</v>
       </c>
       <c r="G60">
-        <v>-6.446451020377535</v>
+        <v>-7.051251274401449</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>0.9082750388478625</v>
       </c>
       <c r="E61">
-        <v>-10.33014414472686</v>
+        <v>-11.35650466466932</v>
       </c>
       <c r="F61">
-        <v>1.328138705376398</v>
+        <v>2.30767321877798</v>
       </c>
       <c r="G61">
-        <v>-6.757864107620158</v>
+        <v>-8.011796130984367</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>0.5746824699886419</v>
       </c>
       <c r="E62">
-        <v>-10.55152765353984</v>
+        <v>-11.19013305810152</v>
       </c>
       <c r="F62">
-        <v>1.447571060777225</v>
+        <v>1.943504684424456</v>
       </c>
       <c r="G62">
-        <v>-7.489180169972859</v>
+        <v>-7.663702199166619</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>0.2755698150440445</v>
       </c>
       <c r="E63">
-        <v>-10.14330383564439</v>
+        <v>-10.52303902355759</v>
       </c>
       <c r="F63">
-        <v>1.389621790746983</v>
+        <v>2.418081339692709</v>
       </c>
       <c r="G63">
-        <v>-6.918478535003438</v>
+        <v>-6.625637608236127</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>0.01484177023916774</v>
       </c>
       <c r="E64">
-        <v>-8.120429967944034</v>
+        <v>-11.34502951153388</v>
       </c>
       <c r="F64">
-        <v>0.9574393224192028</v>
+        <v>2.291443844622332</v>
       </c>
       <c r="G64">
-        <v>-6.665466781619099</v>
+        <v>-8.255290065943301</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-0.204922901429683</v>
       </c>
       <c r="E65">
-        <v>-8.966525523063154</v>
+        <v>-10.67160467032723</v>
       </c>
       <c r="F65">
-        <v>0.6235824080689181</v>
+        <v>2.359775871679263</v>
       </c>
       <c r="G65">
-        <v>-6.353434622360632</v>
+        <v>-7.292576802032161</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-0.3830156329935938</v>
       </c>
       <c r="E66">
-        <v>-8.801272449575249</v>
+        <v>-9.520751871439908</v>
       </c>
       <c r="F66">
-        <v>0.6530871982218309</v>
+        <v>1.906832859502522</v>
       </c>
       <c r="G66">
-        <v>-6.585484001390308</v>
+        <v>-7.946634663134891</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-0.5183873922492421</v>
       </c>
       <c r="E67">
-        <v>-8.256084935317807</v>
+        <v>-9.993343418880386</v>
       </c>
       <c r="F67">
-        <v>0.5006891336591947</v>
+        <v>1.845500536999246</v>
       </c>
       <c r="G67">
-        <v>-6.686892632349262</v>
+        <v>-6.36280677678231</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-0.6111618940014519</v>
       </c>
       <c r="E68">
-        <v>-7.240302930657268</v>
+        <v>-8.090455998487263</v>
       </c>
       <c r="F68">
-        <v>0.4872372754051335</v>
+        <v>2.254006608220211</v>
       </c>
       <c r="G68">
-        <v>-6.300985649381959</v>
+        <v>-7.495642354865517</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-0.6634258936820291</v>
       </c>
       <c r="E69">
-        <v>-8.28714121006241</v>
+        <v>-10.81479048997576</v>
       </c>
       <c r="F69">
-        <v>0.07590564297321935</v>
+        <v>1.474883990782331</v>
       </c>
       <c r="G69">
-        <v>-6.519180395329784</v>
+        <v>-7.263480417287507</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-0.6784667949021679</v>
       </c>
       <c r="E70">
-        <v>-8.023851202782447</v>
+        <v>-8.772077377647797</v>
       </c>
       <c r="F70">
-        <v>0.6086875337991802</v>
+        <v>1.484360513870357</v>
       </c>
       <c r="G70">
-        <v>-7.202771633188352</v>
+        <v>-7.254240684687401</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-0.6602208234209616</v>
       </c>
       <c r="E71">
-        <v>-7.957513587044084</v>
+        <v>-9.722875780298265</v>
       </c>
       <c r="F71">
-        <v>0.4924899531062851</v>
+        <v>1.108859913446536</v>
       </c>
       <c r="G71">
-        <v>-6.134988274951823</v>
+        <v>-7.231020518274953</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-0.6131473101688943</v>
       </c>
       <c r="E72">
-        <v>-8.369006963173074</v>
+        <v>-10.82840761131682</v>
       </c>
       <c r="F72">
-        <v>-0.4910952768949863</v>
+        <v>0.7525409886019395</v>
       </c>
       <c r="G72">
-        <v>-6.015441164983201</v>
+        <v>-6.863473820868448</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-0.5412406606311922</v>
       </c>
       <c r="E73">
-        <v>-8.914063151684294</v>
+        <v>-10.57399341309189</v>
       </c>
       <c r="F73">
-        <v>-0.2033875389220648</v>
+        <v>0.5835987702705916</v>
       </c>
       <c r="G73">
-        <v>-6.573321057079025</v>
+        <v>-6.248503570947893</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-0.4487635584859719</v>
       </c>
       <c r="E74">
-        <v>-8.333023708708126</v>
+        <v>-10.36499075221588</v>
       </c>
       <c r="F74">
-        <v>-1.142090994672256</v>
+        <v>0.9753453121981169</v>
       </c>
       <c r="G74">
-        <v>-5.665741618578908</v>
+        <v>-5.335372347578418</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-0.339805860650073</v>
       </c>
       <c r="E75">
-        <v>-8.319347717204961</v>
+        <v>-10.66125257874569</v>
       </c>
       <c r="F75">
-        <v>0.07293180399716911</v>
+        <v>0.8677685510661564</v>
       </c>
       <c r="G75">
-        <v>-5.484532287395821</v>
+        <v>-7.09798955632488</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-0.2185425970645102</v>
       </c>
       <c r="E76">
-        <v>-10.1404735393896</v>
+        <v>-11.25387132975948</v>
       </c>
       <c r="F76">
-        <v>-0.4167816088224398</v>
+        <v>0.5075745235112641</v>
       </c>
       <c r="G76">
-        <v>-5.913115512909869</v>
+        <v>-6.835185209235376</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-0.08765002829904454</v>
       </c>
       <c r="E77">
-        <v>-9.757101986848239</v>
+        <v>-11.55350234095099</v>
       </c>
       <c r="F77">
-        <v>-0.4802751418796191</v>
+        <v>0.5870340098900011</v>
       </c>
       <c r="G77">
-        <v>-5.463765235227973</v>
+        <v>-5.805201659966245</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>0.05101079083107808</v>
       </c>
       <c r="E78">
-        <v>-10.58492514934641</v>
+        <v>-10.97847671145701</v>
       </c>
       <c r="F78">
-        <v>-0.3638978054603166</v>
+        <v>0.2885260177193796</v>
       </c>
       <c r="G78">
-        <v>-4.972860989937145</v>
+        <v>-5.73105206097765</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>0.1957643651922422</v>
       </c>
       <c r="E79">
-        <v>-9.561920228643638</v>
+        <v>-12.64963758840363</v>
       </c>
       <c r="F79">
-        <v>-0.6350779570125823</v>
+        <v>0.3504290853631839</v>
       </c>
       <c r="G79">
-        <v>-4.224882951885291</v>
+        <v>-6.230461097758865</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>0.3452915565942809</v>
       </c>
       <c r="E80">
-        <v>-12.39245649256002</v>
+        <v>-12.94506164724202</v>
       </c>
       <c r="F80">
-        <v>-1.371482495855495</v>
+        <v>0.2623413241168873</v>
       </c>
       <c r="G80">
-        <v>-4.647583337976053</v>
+        <v>-5.012759684776441</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>0.4986628724026375</v>
       </c>
       <c r="E81">
-        <v>-12.86961274180023</v>
+        <v>-11.86129819077834</v>
       </c>
       <c r="F81">
-        <v>-0.8968296307861842</v>
+        <v>0.5765013183634053</v>
       </c>
       <c r="G81">
-        <v>-4.552107204623473</v>
+        <v>-4.737785772284576</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>0.6539742031402627</v>
       </c>
       <c r="E82">
-        <v>-12.2514035841691</v>
+        <v>-13.43580784697925</v>
       </c>
       <c r="F82">
-        <v>-0.4412921719038744</v>
+        <v>0.58154773258126</v>
       </c>
       <c r="G82">
-        <v>-3.480334639012122</v>
+        <v>-5.712863923784893</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>0.8112240845343611</v>
       </c>
       <c r="E83">
-        <v>-12.76070747038976</v>
+        <v>-13.67607056393021</v>
       </c>
       <c r="F83">
-        <v>-0.9541079232201587</v>
+        <v>0.6497795271824525</v>
       </c>
       <c r="G83">
-        <v>-2.941357961945537</v>
+        <v>-4.230133477110575</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>0.9706607617883877</v>
       </c>
       <c r="E84">
-        <v>-14.12739639743067</v>
+        <v>-15.51096294709816</v>
       </c>
       <c r="F84">
-        <v>-1.188979903140319</v>
+        <v>-0.09548605776820676</v>
       </c>
       <c r="G84">
-        <v>-4.23679098419005</v>
+        <v>-3.105666958150645</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>1.132785936098344</v>
       </c>
       <c r="E85">
-        <v>-15.28643214884985</v>
+        <v>-16.19041518720902</v>
       </c>
       <c r="F85">
-        <v>-0.7085500038038844</v>
+        <v>-0.1269234290718508</v>
       </c>
       <c r="G85">
-        <v>-3.574969893797729</v>
+        <v>-3.171023748186937</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>1.298875684107007</v>
       </c>
       <c r="E86">
-        <v>-15.69339705097117</v>
+        <v>-17.7598801233654</v>
       </c>
       <c r="F86">
-        <v>-1.008110850943464</v>
+        <v>-0.09590106983700931</v>
       </c>
       <c r="G86">
-        <v>-2.705402139179523</v>
+        <v>-2.16769009050894</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>1.471020842608373</v>
       </c>
       <c r="E87">
-        <v>-16.92349814499272</v>
+        <v>-17.69555315008644</v>
       </c>
       <c r="F87">
-        <v>-0.6575656468963805</v>
+        <v>-0.4241631907487862</v>
       </c>
       <c r="G87">
-        <v>-3.080000298584675</v>
+        <v>-3.722213027747893</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>1.649591206991579</v>
       </c>
       <c r="E88">
-        <v>-18.07791938139809</v>
+        <v>-18.95530669191022</v>
       </c>
       <c r="F88">
-        <v>-0.7283305890153339</v>
+        <v>-0.2290586447348215</v>
       </c>
       <c r="G88">
-        <v>-3.460749451601794</v>
+        <v>-2.629908458701983</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>1.838438682152386</v>
       </c>
       <c r="E89">
-        <v>-19.88247551718866</v>
+        <v>-20.40076389584054</v>
       </c>
       <c r="F89">
-        <v>-0.99498951128312</v>
+        <v>-0.660575934038154</v>
       </c>
       <c r="G89">
-        <v>-2.76305860029147</v>
+        <v>-3.035394007988535</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>2.040382192059929</v>
       </c>
       <c r="E90">
-        <v>-20.54353762435437</v>
+        <v>-22.12693214655834</v>
       </c>
       <c r="F90">
-        <v>-0.7056358072808359</v>
+        <v>-0.5728336019988247</v>
       </c>
       <c r="G90">
-        <v>-1.612230207202324</v>
+        <v>-3.012150667757313</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>2.257730985125741</v>
       </c>
       <c r="E91">
-        <v>-22.72806442870653</v>
+        <v>-22.42646805979569</v>
       </c>
       <c r="F91">
-        <v>-0.6790982291647508</v>
+        <v>-0.5551636969297085</v>
       </c>
       <c r="G91">
-        <v>-2.586454237953509</v>
+        <v>-3.752600525252863</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>2.491649137658537</v>
       </c>
       <c r="E92">
-        <v>-24.28844524600352</v>
+        <v>-26.2280902899169</v>
       </c>
       <c r="F92">
-        <v>-0.8116999695352846</v>
+        <v>-0.6777413633589653</v>
       </c>
       <c r="G92">
-        <v>-2.376757662404994</v>
+        <v>-3.72358690414669</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>2.741671544528801</v>
       </c>
       <c r="E93">
-        <v>-26.4432245045993</v>
+        <v>-25.91340210264988</v>
       </c>
       <c r="F93">
-        <v>-1.09698556122242</v>
+        <v>-1.293146275674954</v>
       </c>
       <c r="G93">
-        <v>-2.512549619334819</v>
+        <v>-2.976198143200827</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>3.002717476620259</v>
       </c>
       <c r="E94">
-        <v>-28.01078295319844</v>
+        <v>-27.96308453647564</v>
       </c>
       <c r="F94">
-        <v>-1.135730789753562</v>
+        <v>-0.9507629756476543</v>
       </c>
       <c r="G94">
-        <v>-1.71385733416687</v>
+        <v>-3.65041060554664</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>3.272278189783536</v>
       </c>
       <c r="E95">
-        <v>-29.75076304963963</v>
+        <v>-29.36733262693617</v>
       </c>
       <c r="F95">
-        <v>-1.125830142555302</v>
+        <v>-1.684780988003102</v>
       </c>
       <c r="G95">
-        <v>-3.008204497474501</v>
+        <v>-3.682807604193948</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>3.544504295549347</v>
       </c>
       <c r="E96">
-        <v>-32.29367781543283</v>
+        <v>-32.1983104170683</v>
       </c>
       <c r="F96">
-        <v>-1.610158338889311</v>
+        <v>-1.545999626807684</v>
       </c>
       <c r="G96">
-        <v>-3.221085817831796</v>
+        <v>-3.867605566741605</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>3.812391387412807</v>
       </c>
       <c r="E97">
-        <v>-33.90443111335414</v>
+        <v>-33.37546685722917</v>
       </c>
       <c r="F97">
-        <v>-1.683366964846523</v>
+        <v>-2.038575049003965</v>
       </c>
       <c r="G97">
-        <v>-3.463192634209776</v>
+        <v>-3.817017120356002</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>4.068424564900763</v>
       </c>
       <c r="E98">
-        <v>-35.52162163707735</v>
+        <v>-36.51364273861963</v>
       </c>
       <c r="F98">
-        <v>-0.939472327947497</v>
+        <v>-2.602790997663959</v>
       </c>
       <c r="G98">
-        <v>-2.683059267334982</v>
+        <v>-4.982497988001962</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>4.302215365135687</v>
       </c>
       <c r="E99">
-        <v>-37.44025003312112</v>
+        <v>-38.59220325119231</v>
       </c>
       <c r="F99">
-        <v>-1.597483489259076</v>
+        <v>-2.844297372113141</v>
       </c>
       <c r="G99">
-        <v>-2.782918562981558</v>
+        <v>-5.059968064166448</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>4.50324834132832</v>
       </c>
       <c r="E100">
-        <v>-40.41301434443341</v>
+        <v>-40.58340723592003</v>
       </c>
       <c r="F100">
-        <v>-1.315268655534118</v>
+        <v>-2.347562717187403</v>
       </c>
       <c r="G100">
-        <v>-3.713446703159903</v>
+        <v>-4.510609516288708</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>4.661030358249072</v>
       </c>
       <c r="E101">
-        <v>-41.2177060617004</v>
+        <v>-41.73035196173873</v>
       </c>
       <c r="F101">
-        <v>-1.045093313641448</v>
+        <v>-3.001464347813694</v>
       </c>
       <c r="G101">
-        <v>-3.851056149590788</v>
+        <v>-5.380994975655114</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>4.769991814213182</v>
       </c>
       <c r="E102">
-        <v>-45.8516459647724</v>
+        <v>-44.03901329558915</v>
       </c>
       <c r="F102">
-        <v>-1.782761941141033</v>
+        <v>-3.287351334235262</v>
       </c>
       <c r="G102">
-        <v>-4.851254720643095</v>
+        <v>-5.635403779257026</v>
       </c>
     </row>
   </sheetData>
